--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>80142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R2" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>80111</v>
+        <v>98457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R3" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127155482</v>
+        <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -919,13 +919,8 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466081</v>
+        <v>466371</v>
       </c>
       <c r="R4" t="n">
-        <v>6809216</v>
+        <v>6809222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127153831</v>
+        <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>79012</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,8 +1024,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466371</v>
+        <v>466081</v>
       </c>
       <c r="R5" t="n">
-        <v>6809222</v>
+        <v>6809216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1082,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,37 +1111,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R6" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,42 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R7" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1287,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154595</v>
+        <v>127155380</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1336,14 +1336,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466128</v>
+        <v>466021</v>
       </c>
       <c r="R8" t="n">
-        <v>6809202</v>
+        <v>6809226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127155380</v>
+        <v>127154595</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466021</v>
+        <v>466128</v>
       </c>
       <c r="R10" t="n">
-        <v>6809226</v>
+        <v>6809202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,58 +1722,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
-        <v>98382</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1786,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1837,60 +1828,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153532</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>98457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466439</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809218</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
         <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,45 +2575,53 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2621,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R20" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,13 +2667,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,46 +2696,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>98353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2731,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R21" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,17 +2773,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2798,27 +2798,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155506</v>
+        <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>5196</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,13 +2826,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2886,7 +2889,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2905,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,16 +2918,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2933,11 +2935,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2952,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R23" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,27 +3012,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127153899</v>
+        <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>5196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3043,11 +3041,12 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3057,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R24" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>127154177</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>127153768</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153920</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466298</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809205</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127154119</v>
+        <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466247</v>
+        <v>466298</v>
       </c>
       <c r="R28" t="n">
-        <v>6809203</v>
+        <v>6809205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
         <v>127153894</v>
       </c>
       <c r="B29" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,17 +4067,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97239</v>
+        <v>5176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>97314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
-        <v>79012</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,41 +4609,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153858</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466333</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80049</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>80080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,22 +5104,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127153812</v>
+        <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5159,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466380</v>
+        <v>466062</v>
       </c>
       <c r="R44" t="n">
-        <v>6809217</v>
+        <v>6809234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,42 +1111,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R6" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1182,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,37 +1212,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R7" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1288,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,22 +1727,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,14 +1773,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1815,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
         <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155475</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466076</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127153742</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466410</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>98457</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R18" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2473,46 +2472,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R19" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2563,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127154177</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466206</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127153768</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466392</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3528,46 +3528,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153894</v>
+        <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>98457</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466299</v>
+        <v>466254</v>
       </c>
       <c r="R29" t="n">
-        <v>6809206</v>
+        <v>6809208</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3619,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3638,46 +3637,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127154103</v>
+        <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>98463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3685,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466254</v>
+        <v>466299</v>
       </c>
       <c r="R30" t="n">
-        <v>6809208</v>
+        <v>6809206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,6 +3728,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,41 +4504,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127155517</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4636,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466108</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79046</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4706,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>91343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R43" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5091,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5104,12 +5109,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5119,7 +5124,7 @@
         <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5217,10 +5222,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B45" t="n">
-        <v>91337</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5228,21 +5233,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5298,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,19 +1722,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1773,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127153742</v>
+        <v>127155475</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466410</v>
+        <v>466076</v>
       </c>
       <c r="R17" t="n">
-        <v>6809205</v>
+        <v>6809225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153768</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466392</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809204</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>97320</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4085,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B35" t="n">
-        <v>97320</v>
+        <v>5176</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,38 +4187,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,12 +5104,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -2582,46 +2582,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2629,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R20" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,17 +2659,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2696,38 +2684,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B21" t="n">
-        <v>98359</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2735,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R21" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,13 +2769,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127153920</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466298</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127153768</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466392</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153920</v>
+        <v>127154119</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466298</v>
+        <v>466247</v>
       </c>
       <c r="R28" t="n">
-        <v>6809205</v>
+        <v>6809203</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3528,46 +3528,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127154103</v>
+        <v>127153894</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>98463</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466254</v>
+        <v>466299</v>
       </c>
       <c r="R29" t="n">
-        <v>6809208</v>
+        <v>6809206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,6 +3619,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3637,46 +3638,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153894</v>
+        <v>127154103</v>
       </c>
       <c r="B30" t="n">
-        <v>98463</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3684,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466299</v>
+        <v>466254</v>
       </c>
       <c r="R30" t="n">
-        <v>6809206</v>
+        <v>6809208</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3729,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R43" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5091,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5104,19 +5109,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127155443</v>
+        <v>127153812</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466062</v>
+        <v>466380</v>
       </c>
       <c r="R44" t="n">
-        <v>6809234</v>
+        <v>6809217</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5217,10 +5222,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B45" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5228,21 +5233,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5298,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154078</v>
+        <v>127154595</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466256</v>
+        <v>466128</v>
       </c>
       <c r="R9" t="n">
-        <v>6809224</v>
+        <v>6809202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154595</v>
+        <v>127154078</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466128</v>
+        <v>466256</v>
       </c>
       <c r="R10" t="n">
-        <v>6809202</v>
+        <v>6809224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,19 +1727,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1768,14 +1773,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1815,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
         <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155475</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466076</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127153742</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466410</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R18" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2454,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2472,46 +2473,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B19" t="n">
-        <v>98463</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R19" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2564,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>127154181</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153920</v>
+        <v>127154177</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466298</v>
+        <v>466206</v>
       </c>
       <c r="R26" t="n">
-        <v>6809205</v>
+        <v>6809201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127154119</v>
+        <v>127153920</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466247</v>
+        <v>466298</v>
       </c>
       <c r="R28" t="n">
-        <v>6809203</v>
+        <v>6809205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3528,46 +3528,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153894</v>
+        <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>98463</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466299</v>
+        <v>466254</v>
       </c>
       <c r="R29" t="n">
-        <v>6809206</v>
+        <v>6809208</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3619,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3638,46 +3637,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127154103</v>
+        <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3685,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466254</v>
+        <v>466299</v>
       </c>
       <c r="R30" t="n">
-        <v>6809208</v>
+        <v>6809206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,6 +3728,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97320</v>
+        <v>5176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>97321</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4800,36 +4800,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>80083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4838,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,44 +4914,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>80083</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R42" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,11 +4988,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B43" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,12 +5104,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,19 +1722,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1773,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2582,38 +2582,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2621,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R20" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,13 +2667,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2684,46 +2696,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2731,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R21" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,17 +2773,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -1734,37 +1734,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1772,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1819,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1832,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127153742</v>
+        <v>127155475</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466410</v>
+        <v>466076</v>
       </c>
       <c r="R17" t="n">
-        <v>6809205</v>
+        <v>6809225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>98464</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R18" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2473,46 +2472,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R19" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2563,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153768</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466392</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809204</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3747,7 +3747,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B31" t="n">
         <v>57657</v>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3893,7 +3893,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127155517</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4632,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466108</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809230</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,41 +4710,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80083</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>80083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,7 +5015,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127155443</v>
+        <v>127153812</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466062</v>
+        <v>466380</v>
       </c>
       <c r="R43" t="n">
-        <v>6809234</v>
+        <v>6809217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5116,7 +5116,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127153812</v>
+        <v>127155443</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466380</v>
+        <v>466062</v>
       </c>
       <c r="R44" t="n">
-        <v>6809217</v>
+        <v>6809234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -1734,46 +1734,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1781,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1832,49 +1828,58 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>97321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4085,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B35" t="n">
-        <v>97321</v>
+        <v>5176</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,38 +4187,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154595</v>
+        <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466128</v>
+        <v>466256</v>
       </c>
       <c r="R9" t="n">
-        <v>6809202</v>
+        <v>6809224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154078</v>
+        <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466256</v>
+        <v>466128</v>
       </c>
       <c r="R10" t="n">
-        <v>6809224</v>
+        <v>6809202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,48 +1633,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153879</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466321</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,14 +1777,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1819,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1832,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98464</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
         <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,6 +3193,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3220,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127153920</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466298</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3299,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153920</v>
+        <v>127154119</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466298</v>
+        <v>466247</v>
       </c>
       <c r="R28" t="n">
-        <v>6809205</v>
+        <v>6809203</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
         <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
-        <v>56849</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3893,7 +3893,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97321</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>97325</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,7 +4286,7 @@
         <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,41 +4504,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4609,37 +4605,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,7 +4702,7 @@
         <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>80083</v>
+        <v>80087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>91348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R44" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,6 +5192,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5205,22 +5210,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B45" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5228,21 +5233,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5298,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R2" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,35 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R3" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1633,57 +1633,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153879</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466321</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809223</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1777,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1832,49 +1828,58 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
         <v>79018</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2907,27 +2907,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153899</v>
+        <v>127155506</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>5197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2936,11 +2936,12 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2950,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R23" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,6 +2995,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3012,27 +3014,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127155506</v>
+        <v>127153899</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3041,12 +3043,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3056,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R24" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,7 +3101,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127153768</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466392</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809204</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,11 +3193,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153920</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3263,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466298</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809205</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127154119</v>
+        <v>127153920</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466247</v>
+        <v>466298</v>
       </c>
       <c r="R28" t="n">
-        <v>6809203</v>
+        <v>6809205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4594,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B39" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,41 +4605,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R39" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4706,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R44" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,11 +5192,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5210,22 +5205,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R2" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R3" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,11 +2826,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2845,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R22" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,27 +2903,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155506</v>
+        <v>127155499</v>
       </c>
       <c r="B23" t="n">
-        <v>5197</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2935,13 +2931,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2995,7 +2994,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3014,27 +3012,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127153899</v>
+        <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3043,11 +3041,12 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3057,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R24" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>56853</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B32" t="n">
         <v>57661</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56853</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
         <v>57661</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127155380</v>
+        <v>127154078</v>
       </c>
       <c r="B8" t="n">
         <v>57661</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466021</v>
+        <v>466256</v>
       </c>
       <c r="R8" t="n">
-        <v>6809226</v>
+        <v>6809224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154078</v>
+        <v>127154595</v>
       </c>
       <c r="B9" t="n">
         <v>57661</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466256</v>
+        <v>466128</v>
       </c>
       <c r="R9" t="n">
-        <v>6809224</v>
+        <v>6809202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154595</v>
+        <v>127155380</v>
       </c>
       <c r="B10" t="n">
         <v>57661</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466128</v>
+        <v>466021</v>
       </c>
       <c r="R10" t="n">
-        <v>6809202</v>
+        <v>6809226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,48 +1633,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153879</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466321</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1743,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1768,14 +1777,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1819,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1832,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127153899</v>
+        <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,7 +2826,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2841,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R22" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,16 +2918,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2931,11 +2935,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R23" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127155517</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
         <v>79018</v>
@@ -4632,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466108</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809230</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,41 +4710,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,37 +1111,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R6" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,42 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R7" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1287,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R18" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2454,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2472,46 +2473,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R19" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2564,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B31" t="n">
         <v>57661</v>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B32" t="n">
         <v>57661</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4800,36 +4800,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>80087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4838,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,44 +4914,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>80087</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R42" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,11 +4988,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154078</v>
+        <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466256</v>
+        <v>466021</v>
       </c>
       <c r="R8" t="n">
-        <v>6809224</v>
+        <v>6809226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154595</v>
+        <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466128</v>
+        <v>466256</v>
       </c>
       <c r="R9" t="n">
-        <v>6809202</v>
+        <v>6809224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127155380</v>
+        <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466021</v>
+        <v>466128</v>
       </c>
       <c r="R10" t="n">
-        <v>6809226</v>
+        <v>6809202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,57 +1633,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153879</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466321</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809223</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1832,49 +1828,58 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>98471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127155565</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127153742</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R18" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2473,46 +2472,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>98471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R19" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2563,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,11 +2826,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2845,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R22" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153899</v>
+        <v>127155499</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,16 +2914,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2935,7 +2931,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R23" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
         <v>127154177</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>127153768</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>127154119</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>56855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
         <v>127154111</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,41 +4504,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127155517</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4636,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466108</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4706,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>80087</v>
+        <v>80089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,42 +1111,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R6" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1182,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,37 +1212,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R7" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1288,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>97327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4085,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B35" t="n">
-        <v>97327</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,38 +4187,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80089</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>80089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97327</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>97327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B2" t="n">
-        <v>80151</v>
+        <v>98471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R2" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B3" t="n">
-        <v>98471</v>
+        <v>80151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,35 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R3" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127155380</v>
+        <v>127154078</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466021</v>
+        <v>466256</v>
       </c>
       <c r="R8" t="n">
-        <v>6809226</v>
+        <v>6809224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154078</v>
+        <v>127154595</v>
       </c>
       <c r="B9" t="n">
         <v>57663</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466256</v>
+        <v>466128</v>
       </c>
       <c r="R9" t="n">
-        <v>6809224</v>
+        <v>6809202</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127154595</v>
+        <v>127155380</v>
       </c>
       <c r="B10" t="n">
         <v>57663</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466128</v>
+        <v>466021</v>
       </c>
       <c r="R10" t="n">
-        <v>6809202</v>
+        <v>6809226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,37 +1734,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>98471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1772,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R12" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1819,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,58 +1832,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127153899</v>
+        <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,7 +2826,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2841,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R22" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155499</v>
+        <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,16 +2918,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2931,11 +2935,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R23" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127153920</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466298</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B27" t="n">
         <v>79020</v>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3422,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153920</v>
+        <v>127153768</v>
       </c>
       <c r="B28" t="n">
         <v>79020</v>
@@ -3465,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466298</v>
+        <v>466392</v>
       </c>
       <c r="R28" t="n">
-        <v>6809205</v>
+        <v>6809204</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,6 +3496,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127155517</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4632,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466108</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809230</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,41 +4710,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127154126</v>
       </c>
       <c r="B2" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154078</v>
+        <v>127155380</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466256</v>
+        <v>466021</v>
       </c>
       <c r="R8" t="n">
-        <v>6809224</v>
+        <v>6809226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154595</v>
+        <v>127154078</v>
       </c>
       <c r="B9" t="n">
         <v>57663</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466128</v>
+        <v>466256</v>
       </c>
       <c r="R9" t="n">
-        <v>6809202</v>
+        <v>6809224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127155380</v>
+        <v>127154595</v>
       </c>
       <c r="B10" t="n">
         <v>57663</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466021</v>
+        <v>466128</v>
       </c>
       <c r="R10" t="n">
-        <v>6809226</v>
+        <v>6809202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B11" t="n">
         <v>79020</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R11" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,69 +1727,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153879</v>
+        <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466321</v>
+        <v>466439</v>
       </c>
       <c r="R12" t="n">
-        <v>6809223</v>
+        <v>6809218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,37 +1840,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>98477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155475</v>
       </c>
       <c r="B15" t="n">
         <v>79020</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466076</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
         <v>79020</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127153742</v>
       </c>
       <c r="B17" t="n">
         <v>79020</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466410</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>98477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R18" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2454,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2472,46 +2473,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B19" t="n">
-        <v>98471</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R19" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2564,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153920</v>
+        <v>127154177</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466298</v>
+        <v>466206</v>
       </c>
       <c r="R26" t="n">
-        <v>6809205</v>
+        <v>6809201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B27" t="n">
         <v>79020</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R27" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,6 +3395,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3422,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153768</v>
+        <v>127153920</v>
       </c>
       <c r="B28" t="n">
         <v>79020</v>
@@ -3460,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466392</v>
+        <v>466298</v>
       </c>
       <c r="R28" t="n">
-        <v>6809204</v>
+        <v>6809205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,11 +3501,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56855</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
         <v>57663</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>97333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,43 +4085,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R34" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B35" t="n">
-        <v>97327</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,38 +4187,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R35" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153599</v>
+        <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,41 +4504,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466439</v>
+        <v>466333</v>
       </c>
       <c r="R38" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,7 +4594,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153858</v>
+        <v>127155517</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4636,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466333</v>
+        <v>466108</v>
       </c>
       <c r="R39" t="n">
-        <v>6809211</v>
+        <v>6809230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127155517</v>
+        <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4710,37 +4706,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466108</v>
+        <v>466439</v>
       </c>
       <c r="R40" t="n">
-        <v>6809230</v>
+        <v>6809218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,36 +4800,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>80089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4838,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,44 +4914,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>80089</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R42" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,11 +4988,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>91356</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R43" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5091,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5104,12 +5109,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B45" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5228,21 +5233,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R45" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5298,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>98477</v>
+        <v>80154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R2" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>80151</v>
+        <v>98480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R3" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127153831</v>
+        <v>127155482</v>
       </c>
       <c r="B4" t="n">
-        <v>79052</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -919,8 +919,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -928,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466371</v>
+        <v>466081</v>
       </c>
       <c r="R4" t="n">
-        <v>6809222</v>
+        <v>6809216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +977,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127155482</v>
+        <v>127153831</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>79055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1024,13 +1028,8 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466081</v>
+        <v>466371</v>
       </c>
       <c r="R5" t="n">
-        <v>6809216</v>
+        <v>6809222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,6 +1081,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,37 +1633,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>98480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1671,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1718,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,12 +1731,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1742,7 +1746,7 @@
         <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,46 +1844,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B13" t="n">
-        <v>98477</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R13" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1920,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127153742</v>
+        <v>127155475</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466410</v>
+        <v>466076</v>
       </c>
       <c r="R17" t="n">
-        <v>6809205</v>
+        <v>6809225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,46 +2363,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127154066</v>
+        <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>98477</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466274</v>
+        <v>466144</v>
       </c>
       <c r="R18" t="n">
-        <v>6809202</v>
+        <v>6809220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2473,46 +2472,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127154600</v>
+        <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>98480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2520,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466144</v>
+        <v>466274</v>
       </c>
       <c r="R19" t="n">
-        <v>6809220</v>
+        <v>6809202</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2563,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,27 +2798,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155499</v>
+        <v>127155506</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>5197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,16 +2826,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2889,6 +2886,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2910,7 +2908,7 @@
         <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,27 +3010,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127155506</v>
+        <v>127155499</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3040,13 +3038,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3100,7 +3101,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,10 +3326,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153768</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466392</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809204</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154111</v>
+        <v>127154630</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>56858</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466259</v>
+        <v>466148</v>
       </c>
       <c r="R31" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127155460</v>
+        <v>127154111</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466067</v>
+        <v>466259</v>
       </c>
       <c r="R32" t="n">
-        <v>6809228</v>
+        <v>6809208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127154630</v>
+        <v>127155460</v>
       </c>
       <c r="B33" t="n">
-        <v>56855</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466148</v>
+        <v>466067</v>
       </c>
       <c r="R33" t="n">
-        <v>6809222</v>
+        <v>6809228</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127153911</v>
+        <v>127153408</v>
       </c>
       <c r="B34" t="n">
-        <v>97333</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,38 +4085,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466299</v>
+        <v>466439</v>
       </c>
       <c r="R34" t="n">
-        <v>6809206</v>
+        <v>6809218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127153408</v>
+        <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>97336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,43 +4192,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466439</v>
+        <v>466299</v>
       </c>
       <c r="R35" t="n">
-        <v>6809218</v>
+        <v>6809206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,35 +4294,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R36" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4365,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,26 +4395,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R37" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>127153858</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>127155517</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>127153599</v>
       </c>
       <c r="B40" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,44 +4800,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B41" t="n">
-        <v>80089</v>
+        <v>79023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4846,10 +4838,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R41" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,11 +4874,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,36 +4901,44 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>80092</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R42" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4983,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B43" t="n">
-        <v>91356</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,22 +5104,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>91359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5132,21 +5127,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5159,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R44" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,6 +5192,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5210,12 +5210,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
         <v>127153812</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127153844</v>
       </c>
       <c r="B2" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127154126</v>
       </c>
       <c r="B3" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127155482</v>
+        <v>127153831</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>79061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -919,13 +919,8 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466081</v>
+        <v>466371</v>
       </c>
       <c r="R4" t="n">
-        <v>6809216</v>
+        <v>6809222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127153831</v>
+        <v>127155482</v>
       </c>
       <c r="B5" t="n">
-        <v>79055</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1028,8 +1024,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466371</v>
+        <v>466081</v>
       </c>
       <c r="R5" t="n">
-        <v>6809222</v>
+        <v>6809216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1082,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>127153848</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>127153643</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127155380</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127154078</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>127154595</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,46 +1633,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153879</v>
+        <v>127153712</v>
       </c>
       <c r="B11" t="n">
-        <v>98480</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466321</v>
+        <v>466164</v>
       </c>
       <c r="R11" t="n">
-        <v>6809223</v>
+        <v>6809202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,6 +1709,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1731,12 +1727,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1746,7 +1742,7 @@
         <v>127153532</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,37 +1840,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127153712</v>
+        <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>98488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466164</v>
+        <v>466321</v>
       </c>
       <c r="R13" t="n">
-        <v>6809202</v>
+        <v>6809223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,11 +1925,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155565</v>
+        <v>127155475</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466242</v>
+        <v>466076</v>
       </c>
       <c r="R15" t="n">
-        <v>6809226</v>
+        <v>6809225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127153742</v>
+        <v>127155565</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466410</v>
+        <v>466242</v>
       </c>
       <c r="R16" t="n">
-        <v>6809205</v>
+        <v>6809226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127155475</v>
+        <v>127153742</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466076</v>
+        <v>466410</v>
       </c>
       <c r="R17" t="n">
-        <v>6809225</v>
+        <v>6809205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
         <v>127154600</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>127153709</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>127154181</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2798,27 +2798,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127155506</v>
+        <v>127153899</v>
       </c>
       <c r="B22" t="n">
-        <v>5197</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2827,12 +2827,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2842,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R22" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,7 +2885,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2905,27 +2903,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153899</v>
+        <v>127155506</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>5197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2934,11 +2932,12 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2948,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R23" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,6 +2991,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>127155499</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154177</v>
+        <v>127154119</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466206</v>
+        <v>466247</v>
       </c>
       <c r="R25" t="n">
-        <v>6809201</v>
+        <v>6809203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127153768</v>
+        <v>127154177</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466392</v>
+        <v>466206</v>
       </c>
       <c r="R26" t="n">
-        <v>6809204</v>
+        <v>6809201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127154119</v>
+        <v>127153768</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466247</v>
+        <v>466392</v>
       </c>
       <c r="R27" t="n">
-        <v>6809203</v>
+        <v>6809204</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,6 +3395,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,7 +3430,7 @@
         <v>127153920</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>127154103</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127154630</v>
+        <v>127154111</v>
       </c>
       <c r="B31" t="n">
-        <v>56858</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3784,7 +3784,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466148</v>
+        <v>466259</v>
       </c>
       <c r="R31" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127154111</v>
+        <v>127155460</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466259</v>
+        <v>466067</v>
       </c>
       <c r="R32" t="n">
-        <v>6809208</v>
+        <v>6809228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127155460</v>
+        <v>127154630</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>56864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466067</v>
+        <v>466148</v>
       </c>
       <c r="R33" t="n">
-        <v>6809228</v>
+        <v>6809222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>127153801</v>
       </c>
       <c r="B36" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>127153754</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153858</v>
+        <v>127153599</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4504,37 +4504,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466333</v>
+        <v>466439</v>
       </c>
       <c r="R38" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127155517</v>
+        <v>127153858</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4632,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466108</v>
+        <v>466333</v>
       </c>
       <c r="R39" t="n">
-        <v>6809230</v>
+        <v>6809211</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153599</v>
+        <v>127155517</v>
       </c>
       <c r="B40" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,41 +4710,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466439</v>
+        <v>466108</v>
       </c>
       <c r="R40" t="n">
-        <v>6809218</v>
+        <v>6809230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,36 +4800,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153795</v>
+        <v>127154614</v>
       </c>
       <c r="B41" t="n">
-        <v>79023</v>
+        <v>80098</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4838,10 +4846,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466388</v>
+        <v>466148</v>
       </c>
       <c r="R41" t="n">
-        <v>6809208</v>
+        <v>6809222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,6 +4882,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,44 +4914,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127154614</v>
+        <v>127153795</v>
       </c>
       <c r="B42" t="n">
-        <v>80092</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466148</v>
+        <v>466388</v>
       </c>
       <c r="R42" t="n">
-        <v>6809222</v>
+        <v>6809208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,11 +4988,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>sälg intill bäck</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127155443</v>
+        <v>127153697</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>91367</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466062</v>
+        <v>466269</v>
       </c>
       <c r="R43" t="n">
-        <v>6809234</v>
+        <v>6809223</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,6 +5091,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5104,22 +5109,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127153697</v>
+        <v>127155443</v>
       </c>
       <c r="B44" t="n">
-        <v>91359</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5127,21 +5132,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466269</v>
+        <v>466062</v>
       </c>
       <c r="R44" t="n">
-        <v>6809223</v>
+        <v>6809234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5192,11 +5197,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5210,12 +5210,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
         <v>127153812</v>
       </c>
       <c r="B45" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31124-2025 artfynd.xlsx
+++ b/artfynd/A 31124-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153844</v>
+        <v>127154126</v>
       </c>
       <c r="B2" t="n">
-        <v>80160</v>
+        <v>98489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466359</v>
+        <v>466247</v>
       </c>
       <c r="R2" t="n">
-        <v>6809211</v>
+        <v>6809203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127154126</v>
+        <v>127153844</v>
       </c>
       <c r="B3" t="n">
-        <v>98488</v>
+        <v>80160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,35 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466247</v>
+        <v>466359</v>
       </c>
       <c r="R3" t="n">
-        <v>6809203</v>
+        <v>6809211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153848</v>
+        <v>127153643</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,37 +1111,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466359</v>
+        <v>466439</v>
       </c>
       <c r="R6" t="n">
-        <v>6809211</v>
+        <v>6809218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153643</v>
+        <v>127153848</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,42 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466439</v>
+        <v>466359</v>
       </c>
       <c r="R7" t="n">
-        <v>6809218</v>
+        <v>6809211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1287,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153712</v>
+        <v>127153532</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1667,14 +1667,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Itavsberget, Dlr</t>
+          <t>Norr Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466164</v>
+        <v>466439</v>
       </c>
       <c r="R11" t="n">
-        <v>6809202</v>
+        <v>6809218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Måttligt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1727,19 +1722,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127153532</v>
+        <v>127153712</v>
       </c>
       <c r="B12" t="n">
         <v>79029</v>
@@ -1773,14 +1768,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr Itavsberget, Dlr</t>
+          <t>N Itavsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466439</v>
+        <v>466164</v>
       </c>
       <c r="R12" t="n">
-        <v>6809218</v>
+        <v>6809202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,6 +1810,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1828,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
         <v>127153879</v>
       </c>
       <c r="B13" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127154092</v>
       </c>
       <c r="B14" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155475</v>
+        <v>127155565</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466076</v>
+        <v>466242</v>
       </c>
       <c r="R15" t="n">
-        <v>6809225</v>
+        <v>6809226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127155565</v>
+        <v>127153742</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466242</v>
+        <v>466410</v>
       </c>
       <c r="R16" t="n">
-        <v>6809226</v>
+        <v>6809205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127153742</v>
+        <v>127155475</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466410</v>
+        <v>466076</v>
       </c>
       <c r="R17" t="n">
-        <v>6809205</v>
+        <v>6809225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
         <v>127154066</v>
       </c>
       <c r="B19" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,46 +2582,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127153709</v>
+        <v>127154181</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2629,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466410</v>
+        <v>466206</v>
       </c>
       <c r="R20" t="n">
-        <v>6809209</v>
+        <v>6809201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,17 +2659,13 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2696,38 +2684,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127154181</v>
+        <v>127153709</v>
       </c>
       <c r="B21" t="n">
-        <v>98384</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2735,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466206</v>
+        <v>466410</v>
       </c>
       <c r="R21" t="n">
-        <v>6809201</v>
+        <v>6809209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,13 +2769,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127153899</v>
+        <v>127155499</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2826,7 +2826,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -2841,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466299</v>
+        <v>466085</v>
       </c>
       <c r="R22" t="n">
-        <v>6809206</v>
+        <v>6809224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,27 +2907,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127155506</v>
+        <v>127153899</v>
       </c>
       <c r="B23" t="n">
-        <v>5197</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2932,12 +2936,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2947,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466085</v>
+        <v>466299</v>
       </c>
       <c r="R23" t="n">
-        <v>6809224</v>
+        <v>6809206</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,7 +2994,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3010,27 +3012,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127155499</v>
+        <v>127155506</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3038,16 +3040,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3101,6 +3100,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127154119</v>
+        <v>127154177</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466247</v>
+        <v>466206</v>
       </c>
       <c r="R25" t="n">
-        <v>6809203</v>
+        <v>6809201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127154177</v>
+        <v>127153768</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466206</v>
+        <v>466392</v>
       </c>
       <c r="R26" t="n">
-        <v>6809201</v>
+        <v>6809204</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikl</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,7 +3326,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127153768</v>
+        <v>127154119</v>
       </c>
       <c r="B27" t="n">
         <v>79029</v>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466392</v>
+        <v>466247</v>
       </c>
       <c r="R27" t="n">
-        <v>6809204</v>
+        <v>6809203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,11 +3400,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rikl</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,7 +3640,7 @@
         <v>127153894</v>
       </c>
       <c r="B30" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>127153911</v>
       </c>
       <c r="B35" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127153801</v>
+        <v>127153754</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,26 +4294,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4321,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466383</v>
+        <v>466399</v>
       </c>
       <c r="R36" t="n">
-        <v>6809213</v>
+        <v>6809202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,7 +4374,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127153754</v>
+        <v>127153801</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4395,35 +4403,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466399</v>
+        <v>466383</v>
       </c>
       <c r="R37" t="n">
-        <v>6809202</v>
+        <v>6809213</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127153697</v>
+        <v>127153812</v>
       </c>
       <c r="B43" t="n">
-        <v>91367</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5026,21 +5026,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466269</v>
+        <v>466380</v>
       </c>
       <c r="R43" t="n">
-        <v>6809223</v>
+        <v>6809217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,11 +5091,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en högstubbe</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,12 +5104,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127153812</v>
+        <v>127153697</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5255,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466380</v>
+        <v>466269</v>
       </c>
       <c r="R45" t="n">
-        <v>6809217</v>
+        <v>6809223</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,6 +5293,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en högstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5311,12 +5311,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
